--- a/output/2026-10-04_17_Malesia_Sarawak_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-04_17_Malesia_Sarawak_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore storico dal 1961; distributore unico Lincoln Electric (saldatura) per East Malaysia; dealer ufficiale JCB per Sarawak/Sabah. Email reperita e HR generica, non commerciale. Fonti: pansar.com.my, theedgemarkets.com</t>
+          <t>Distributore storico dal 1961; distributore unico Lincoln Electric (saldatura) per East Malaysia; dealer ufficiale JCB per Sarawak/Sabah. Email reperita e HR generica, non commerciale. Fonti: pansar.com.my, theedgemarkets.com [DUPLICATO — vedi anche: 2026-10-04_11_Malesia_Sarawak_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -516,7 +516,6 @@
           <t>KTS Trading Sdn Bhd (incl. KTS Machines &amp; Equipment Sdn Bhd)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Kuching, Sarawak</t>
@@ -527,8 +526,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Distributore unico autorizzato Atlas Copco (compressori, generatori, attrezzature pneumatiche) per Sarawak-Sabah da oltre 40 anni. Tel/email non reperiti da fonti pubbliche. Fonte: theborneopost.com</t>
@@ -536,7 +533,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -546,7 +543,6 @@
           <t>HLM Machinery Sdn Bhd</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Bintulu, Sarawak (filiali Kuching, Miri, Sibu)</t>
@@ -557,11 +553,9 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dealer autorizzato SANY (macchinari pesanti, ricambi) dal 2018. Tel/email non reperiti. Fonte: my.hiredly.com</t>
+          <t>Dealer autorizzato SANY (macchinari pesanti, ricambi) dal 2018. Tel/email non reperiti. Fonte: my.hiredly.com [DUPLICATO — vedi anche: 2026-10-04_Malesia_Sarawak_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -603,7 +597,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Distributore cuscinetti industriali (SKF, Timken e altri), gruppo SLS Bearings dal 1963. Fonte: noonsite.com, my.hiredly.com</t>
+          <t>Distributore cuscinetti industriali (SKF, Timken e altri), gruppo SLS Bearings dal 1963. Fonte: noonsite.com, my.hiredly.com [DUPLICATO — vedi anche: 2026-10-01_19_Malesia_Kelantan_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -618,7 +612,6 @@
           <t>Sara Besi Hardware &amp; Engineering Sdn Bhd</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Kuching, Sarawak</t>
@@ -629,8 +622,6 @@
           <t>Metalworking / Lavorazioni Metalliche (hardware/power tools)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Rivenditore materiali edili, hardware e power tools. Rilevanza per metalworking limitata a utensili elettrici. Tel/email non reperiti. Fonte: magicpin.com</t>
@@ -638,7 +629,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -648,7 +639,6 @@
           <t>Sin Yew Seng Hardware &amp; Machineries Sdn Bhd</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Sibu, Sarawak</t>
@@ -659,8 +649,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Grossista macchinari e attrezzature industriali, attivo dal 1990. Tel/email non reperiti. Fonte: emis.com</t>
@@ -668,7 +656,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -698,7 +686,6 @@
           <t>+60 19-335 0455</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Ufficio vendite riduttori/trasmissioni di potenza Sumitomo Drive per Sarawak. Email non verificabile. Fonte: gearbox.sumitomodrive.com</t>
@@ -706,7 +693,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -716,7 +703,6 @@
           <t>Miri Industrial Sdn Bhd</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Piasau Business Park, Miri, Sarawak</t>
@@ -727,11 +713,9 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Trading ricambi aftermarket per macchine movimento terra (CAT, Komatsu, Hitachi, Kobelco), oltre 30 anni. Tel/email non reperiti. Fonte: sgpgrid.com</t>
+          <t>Trading ricambi aftermarket per macchine movimento terra (CAT, Komatsu, Hitachi, Kobelco), oltre 30 anni. Tel/email non reperiti. Fonte: sgpgrid.com [DUPLICATO — vedi anche: 2026-10-04_Malesia_Sarawak_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -778,7 +762,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -815,7 +799,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Procurement/distribuzione valvole, raccordi, strumentazione, materiali industriali oil&amp;gas, hardware e tools. Fonte: setiatanjong.com</t>
+          <t>Procurement/distribuzione valvole, raccordi, strumentazione, materiali industriali oil&amp;gas, hardware e tools. Fonte: setiatanjong.com [DUPLICATO — vedi anche: 2026-10-04_14_Malesia_Sarawak_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
